--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/47.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/47.xlsx
@@ -426,13 +426,13 @@
         <v>-10.05484638007021</v>
       </c>
       <c r="E2">
-        <v>-13.85364108671898</v>
+        <v>-13.40983252007126</v>
       </c>
       <c r="F2">
-        <v>3.53326101530271</v>
+        <v>0.8447846691080813</v>
       </c>
       <c r="G2">
-        <v>-14.72572586500689</v>
+        <v>-13.8909552099009</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.243896717789484</v>
       </c>
       <c r="E3">
-        <v>-14.13730469855945</v>
+        <v>-13.92972850699586</v>
       </c>
       <c r="F3">
-        <v>3.431946711735914</v>
+        <v>1.914568154309864</v>
       </c>
       <c r="G3">
-        <v>-14.32435700019093</v>
+        <v>-12.18986167317329</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.29184401699313</v>
       </c>
       <c r="E4">
-        <v>-14.3235427205989</v>
+        <v>-15.13581057488073</v>
       </c>
       <c r="F4">
-        <v>3.322512750886877</v>
+        <v>1.230313485310194</v>
       </c>
       <c r="G4">
-        <v>-13.81641405912421</v>
+        <v>-12.30665347336017</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.281484337052901</v>
       </c>
       <c r="E5">
-        <v>-14.34948181971484</v>
+        <v>-16.58127683575907</v>
       </c>
       <c r="F5">
-        <v>3.135149298252073</v>
+        <v>2.151620397234193</v>
       </c>
       <c r="G5">
-        <v>-12.63594046295824</v>
+        <v>-12.02448482535572</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.22988752864515</v>
       </c>
       <c r="E6">
-        <v>-13.71498826955213</v>
+        <v>-15.64698472086656</v>
       </c>
       <c r="F6">
-        <v>3.29524952292594</v>
+        <v>1.540558615211081</v>
       </c>
       <c r="G6">
-        <v>-12.1022793073086</v>
+        <v>-12.11971571867548</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.179004646905541</v>
       </c>
       <c r="E7">
-        <v>-15.31689066502544</v>
+        <v>-16.89558915968345</v>
       </c>
       <c r="F7">
-        <v>3.585002500016373</v>
+        <v>1.752183292339077</v>
       </c>
       <c r="G7">
-        <v>-12.49562230419015</v>
+        <v>-11.81291822164584</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.155861700511366</v>
       </c>
       <c r="E8">
-        <v>-15.85178042938944</v>
+        <v>-16.9316901544726</v>
       </c>
       <c r="F8">
-        <v>2.836633850774827</v>
+        <v>1.355206438630275</v>
       </c>
       <c r="G8">
-        <v>-11.25332885323346</v>
+        <v>-11.02197320229858</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.198325027803703</v>
       </c>
       <c r="E9">
-        <v>-15.02450974072021</v>
+        <v>-15.0489499149396</v>
       </c>
       <c r="F9">
-        <v>3.69168462435331</v>
+        <v>2.011256854299428</v>
       </c>
       <c r="G9">
-        <v>-10.95707392107432</v>
+        <v>-9.989769805350017</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.32912329018803</v>
       </c>
       <c r="E10">
-        <v>-17.6420990428999</v>
+        <v>-18.37617373649127</v>
       </c>
       <c r="F10">
-        <v>3.516980282368089</v>
+        <v>1.781388213492176</v>
       </c>
       <c r="G10">
-        <v>-10.39567003713957</v>
+        <v>-8.080010264771088</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.57020220427405</v>
       </c>
       <c r="E11">
-        <v>-17.58120465291875</v>
+        <v>-20.06779425900455</v>
       </c>
       <c r="F11">
-        <v>3.512934535972816</v>
+        <v>1.623178323231498</v>
       </c>
       <c r="G11">
-        <v>-10.82351835994024</v>
+        <v>-11.4012003840314</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.9360285154885538</v>
       </c>
       <c r="E12">
-        <v>-19.79711378214407</v>
+        <v>-19.82599186089099</v>
       </c>
       <c r="F12">
-        <v>3.391671488611802</v>
+        <v>1.7526637454327</v>
       </c>
       <c r="G12">
-        <v>-9.305284019498934</v>
+        <v>-8.993791094417729</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.4347852935829294</v>
       </c>
       <c r="E13">
-        <v>-20.08314578589055</v>
+        <v>-20.52026126795494</v>
       </c>
       <c r="F13">
-        <v>3.780314966248441</v>
+        <v>2.086636631219377</v>
       </c>
       <c r="G13">
-        <v>-9.212750290301033</v>
+        <v>-7.329335677622885</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.0776744943965324</v>
       </c>
       <c r="E14">
-        <v>-18.95053820878014</v>
+        <v>-20.37972913407491</v>
       </c>
       <c r="F14">
-        <v>3.669189479162887</v>
+        <v>2.401744277774698</v>
       </c>
       <c r="G14">
-        <v>-8.456369658860956</v>
+        <v>-7.942976608783998</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.1361458913047371</v>
       </c>
       <c r="E15">
-        <v>-20.43476367869013</v>
+        <v>-21.38966035031754</v>
       </c>
       <c r="F15">
-        <v>4.171650637944177</v>
+        <v>2.270356924016668</v>
       </c>
       <c r="G15">
-        <v>-8.65330201441571</v>
+        <v>-7.792775410678857</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.2138615550912994</v>
       </c>
       <c r="E16">
-        <v>-21.92294703488282</v>
+        <v>-23.33980692545471</v>
       </c>
       <c r="F16">
-        <v>4.357776509679198</v>
+        <v>2.395604418585147</v>
       </c>
       <c r="G16">
-        <v>-8.335345082862398</v>
+        <v>-6.724324359163112</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1686541898807078</v>
       </c>
       <c r="E17">
-        <v>-22.52826815548812</v>
+        <v>-25.37656962293659</v>
       </c>
       <c r="F17">
-        <v>4.170709612574597</v>
+        <v>2.933509761797423</v>
       </c>
       <c r="G17">
-        <v>-7.738907596337453</v>
+        <v>-6.918720330452414</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.01865394674323756</v>
       </c>
       <c r="E18">
-        <v>-21.57931284175877</v>
+        <v>-25.24484084252747</v>
       </c>
       <c r="F18">
-        <v>4.892225904086994</v>
+        <v>2.267447697698036</v>
       </c>
       <c r="G18">
-        <v>-6.869748098677702</v>
+        <v>-6.571160217989792</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.2184967544445386</v>
       </c>
       <c r="E19">
-        <v>-22.37691296872975</v>
+        <v>-26.16046658756036</v>
       </c>
       <c r="F19">
-        <v>5.00180731433373</v>
+        <v>2.162743714718984</v>
       </c>
       <c r="G19">
-        <v>-7.416202737187625</v>
+        <v>-6.078675111689615</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.5226851564819658</v>
       </c>
       <c r="E20">
-        <v>-24.63889932098312</v>
+        <v>-25.01088176139519</v>
       </c>
       <c r="F20">
-        <v>4.682357365852934</v>
+        <v>3.192293395166795</v>
       </c>
       <c r="G20">
-        <v>-7.859262803137885</v>
+        <v>-6.151544480081764</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.8761330594574763</v>
       </c>
       <c r="E21">
-        <v>-25.11061687294012</v>
+        <v>-26.00600486763273</v>
       </c>
       <c r="F21">
-        <v>4.42388354189221</v>
+        <v>2.744004151058981</v>
       </c>
       <c r="G21">
-        <v>-6.485412054976823</v>
+        <v>-5.49672421834962</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.262334460699398</v>
       </c>
       <c r="E22">
-        <v>-25.56821917141521</v>
+        <v>-27.09552401456017</v>
       </c>
       <c r="F22">
-        <v>5.021731207105864</v>
+        <v>3.056472619068982</v>
       </c>
       <c r="G22">
-        <v>-6.030870994790066</v>
+        <v>-5.952147927135868</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.667617591468803</v>
       </c>
       <c r="E23">
-        <v>-25.50613379277005</v>
+        <v>-28.2413094510329</v>
       </c>
       <c r="F23">
-        <v>4.465739290020863</v>
+        <v>3.643023009643256</v>
       </c>
       <c r="G23">
-        <v>-5.549709384091533</v>
+        <v>-5.829538521124097</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.080850974064815</v>
       </c>
       <c r="E24">
-        <v>-25.44888482436508</v>
+        <v>-27.35130581193541</v>
       </c>
       <c r="F24">
-        <v>4.835056956150189</v>
+        <v>3.319981260103922</v>
       </c>
       <c r="G24">
-        <v>-5.228300607457686</v>
+        <v>-4.847229379208454</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.490492919851699</v>
       </c>
       <c r="E25">
-        <v>-25.95884986779086</v>
+        <v>-28.38920941212342</v>
       </c>
       <c r="F25">
-        <v>4.617863993340576</v>
+        <v>2.981561698099017</v>
       </c>
       <c r="G25">
-        <v>-4.669206703500781</v>
+        <v>-4.722992487303199</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.891656797740064</v>
       </c>
       <c r="E26">
-        <v>-26.422977697311</v>
+        <v>-28.44505908206002</v>
       </c>
       <c r="F26">
-        <v>4.764370708934502</v>
+        <v>3.458426304133803</v>
       </c>
       <c r="G26">
-        <v>-4.844141749721017</v>
+        <v>-4.188176341664627</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.279457815889427</v>
       </c>
       <c r="E27">
-        <v>-26.46554082450909</v>
+        <v>-27.88068442343208</v>
       </c>
       <c r="F27">
-        <v>4.58012357446903</v>
+        <v>3.756988140185606</v>
       </c>
       <c r="G27">
-        <v>-3.69534014465759</v>
+        <v>-3.353102173564387</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.650188539947027</v>
       </c>
       <c r="E28">
-        <v>-25.95376439148025</v>
+        <v>-25.75147745755761</v>
       </c>
       <c r="F28">
-        <v>5.034135180595383</v>
+        <v>3.817803561429535</v>
       </c>
       <c r="G28">
-        <v>-3.572054807004573</v>
+        <v>-3.214647748642058</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.000457302970647</v>
       </c>
       <c r="E29">
-        <v>-25.60918374728859</v>
+        <v>-28.17632584902283</v>
       </c>
       <c r="F29">
-        <v>4.536826467059506</v>
+        <v>3.01715001845809</v>
       </c>
       <c r="G29">
-        <v>-5.002710062802742</v>
+        <v>-3.200876461757069</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.324509473816439</v>
       </c>
       <c r="E30">
-        <v>-24.59270435763088</v>
+        <v>-26.97603117091977</v>
       </c>
       <c r="F30">
-        <v>4.812086328070559</v>
+        <v>3.52618013074358</v>
       </c>
       <c r="G30">
-        <v>-3.915779171464205</v>
+        <v>-3.593481183787747</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.620291097886318</v>
       </c>
       <c r="E31">
-        <v>-25.84996723875043</v>
+        <v>-27.36447914282372</v>
       </c>
       <c r="F31">
-        <v>4.655836355084905</v>
+        <v>3.165532157851954</v>
       </c>
       <c r="G31">
-        <v>-4.149284022520528</v>
+        <v>-4.779777307610949</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.885836946672416</v>
       </c>
       <c r="E32">
-        <v>-24.33470360799187</v>
+        <v>-26.46817639638156</v>
       </c>
       <c r="F32">
-        <v>4.444943954740984</v>
+        <v>3.122780116193471</v>
       </c>
       <c r="G32">
-        <v>-4.633717011113827</v>
+        <v>-1.299982781831758</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.118363629938155</v>
       </c>
       <c r="E33">
-        <v>-25.63397261400658</v>
+        <v>-26.63206639919316</v>
       </c>
       <c r="F33">
-        <v>4.772651069492886</v>
+        <v>2.512709061584108</v>
       </c>
       <c r="G33">
-        <v>-5.105947136727552</v>
+        <v>-2.867625756515185</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.313956246595331</v>
       </c>
       <c r="E34">
-        <v>-24.69983446723033</v>
+        <v>-25.09097688116885</v>
       </c>
       <c r="F34">
-        <v>4.704483059181709</v>
+        <v>3.378361281183619</v>
       </c>
       <c r="G34">
-        <v>-4.51327321133129</v>
+        <v>-2.519717834567262</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.468534491321251</v>
       </c>
       <c r="E35">
-        <v>-24.33178727073093</v>
+        <v>-25.47469259773479</v>
       </c>
       <c r="F35">
-        <v>4.184405839212484</v>
+        <v>2.579999002448317</v>
       </c>
       <c r="G35">
-        <v>-4.362163114854183</v>
+        <v>-2.924066048559193</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.578404930467735</v>
       </c>
       <c r="E36">
-        <v>-24.35142273402819</v>
+        <v>-24.17437751422431</v>
       </c>
       <c r="F36">
-        <v>4.903504954643513</v>
+        <v>2.959194121488625</v>
       </c>
       <c r="G36">
-        <v>-4.739116410046311</v>
+        <v>-3.177871817403802</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.641984478950931</v>
       </c>
       <c r="E37">
-        <v>-23.52953187248007</v>
+        <v>-23.76543819743565</v>
       </c>
       <c r="F37">
-        <v>4.530476202549645</v>
+        <v>3.339901839406444</v>
       </c>
       <c r="G37">
-        <v>-5.885119133119532</v>
+        <v>-4.520990644439104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.657640921056278</v>
       </c>
       <c r="E38">
-        <v>-21.91670679770025</v>
+        <v>-24.27785314529958</v>
       </c>
       <c r="F38">
-        <v>4.95741676195251</v>
+        <v>2.822480365330594</v>
       </c>
       <c r="G38">
-        <v>-5.208206406627646</v>
+        <v>-4.625264584376698</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.623903131556673</v>
       </c>
       <c r="E39">
-        <v>-23.45376144538373</v>
+        <v>-23.13822190500326</v>
       </c>
       <c r="F39">
-        <v>5.448252612602912</v>
+        <v>3.638809933032618</v>
       </c>
       <c r="G39">
-        <v>-5.428822619398471</v>
+        <v>-4.568568357051053</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.541855232517726</v>
       </c>
       <c r="E40">
-        <v>-21.55268541459367</v>
+        <v>-22.55221472604068</v>
       </c>
       <c r="F40">
-        <v>5.011948188078802</v>
+        <v>3.706905047012348</v>
       </c>
       <c r="G40">
-        <v>-6.358589560482725</v>
+        <v>-6.425795540463272</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.414369744721507</v>
       </c>
       <c r="E41">
-        <v>-23.15750867580193</v>
+        <v>-21.69816717056409</v>
       </c>
       <c r="F41">
-        <v>4.975162048455281</v>
+        <v>3.52696707977624</v>
       </c>
       <c r="G41">
-        <v>-6.282954122315966</v>
+        <v>-4.717676908376899</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.247605387484503</v>
       </c>
       <c r="E42">
-        <v>-21.00999308951446</v>
+        <v>-19.61654540956222</v>
       </c>
       <c r="F42">
-        <v>5.093192806210571</v>
+        <v>3.580421628278892</v>
       </c>
       <c r="G42">
-        <v>-6.896027402147294</v>
+        <v>-5.350614703529106</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.047368925480434</v>
       </c>
       <c r="E43">
-        <v>-20.82419432945375</v>
+        <v>-17.84142435482151</v>
       </c>
       <c r="F43">
-        <v>5.096584142357632</v>
+        <v>3.955310893559447</v>
       </c>
       <c r="G43">
-        <v>-6.253344378963536</v>
+        <v>-6.225476964259173</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.819696334292656</v>
       </c>
       <c r="E44">
-        <v>-20.07941432330824</v>
+        <v>-19.17790383175725</v>
       </c>
       <c r="F44">
-        <v>5.11729332742762</v>
+        <v>3.237974543961576</v>
       </c>
       <c r="G44">
-        <v>-6.58665086497193</v>
+        <v>-4.219895910479779</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.569384900685961</v>
       </c>
       <c r="E45">
-        <v>-19.7500765226264</v>
+        <v>-20.30796640647536</v>
       </c>
       <c r="F45">
-        <v>5.264643321037596</v>
+        <v>3.78155751735264</v>
       </c>
       <c r="G45">
-        <v>-6.434162655439856</v>
+        <v>-6.06056604990304</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.304088226135191</v>
       </c>
       <c r="E46">
-        <v>-18.42494993002789</v>
+        <v>-18.42254078185581</v>
       </c>
       <c r="F46">
-        <v>5.878859526130568</v>
+        <v>2.941982303593257</v>
       </c>
       <c r="G46">
-        <v>-7.226449694404937</v>
+        <v>-4.912679905654699</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.029604433290459</v>
       </c>
       <c r="E47">
-        <v>-18.91356774698152</v>
+        <v>-18.54201098312617</v>
       </c>
       <c r="F47">
-        <v>5.591616502270617</v>
+        <v>3.871642472407086</v>
       </c>
       <c r="G47">
-        <v>-7.548668932763968</v>
+        <v>-5.327977555990497</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.750019457205594</v>
       </c>
       <c r="E48">
-        <v>-17.28054114965349</v>
+        <v>-19.33973337889536</v>
       </c>
       <c r="F48">
-        <v>5.607685173150122</v>
+        <v>3.995567892600698</v>
       </c>
       <c r="G48">
-        <v>-7.362797575086103</v>
+        <v>-7.034681981584749</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.468155595694639</v>
       </c>
       <c r="E49">
-        <v>-16.91514311044857</v>
+        <v>-18.52102603457463</v>
       </c>
       <c r="F49">
-        <v>5.353281946606755</v>
+        <v>4.415808616449721</v>
       </c>
       <c r="G49">
-        <v>-9.027302210204336</v>
+        <v>-6.317354449145184</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.184301486791511</v>
       </c>
       <c r="E50">
-        <v>-16.90426571588215</v>
+        <v>-16.17373681743878</v>
       </c>
       <c r="F50">
-        <v>5.623301555427698</v>
+        <v>4.452144124206118</v>
       </c>
       <c r="G50">
-        <v>-8.233115343956337</v>
+        <v>-6.699452699742521</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.902206163608776</v>
       </c>
       <c r="E51">
-        <v>-16.448397822952</v>
+        <v>-14.92380553573763</v>
       </c>
       <c r="F51">
-        <v>5.249338404903472</v>
+        <v>4.298849766113652</v>
       </c>
       <c r="G51">
-        <v>-6.142688463092822</v>
+        <v>-5.961076130999118</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.623606846802792</v>
       </c>
       <c r="E52">
-        <v>-15.52169543049634</v>
+        <v>-15.80343444088355</v>
       </c>
       <c r="F52">
-        <v>5.773188010025046</v>
+        <v>4.364531017481625</v>
       </c>
       <c r="G52">
-        <v>-8.55473083754843</v>
+        <v>-7.381907409448308</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.348859202415916</v>
       </c>
       <c r="E53">
-        <v>-15.90054756597804</v>
+        <v>-14.24197131829874</v>
       </c>
       <c r="F53">
-        <v>5.963099520790861</v>
+        <v>5.093378360508798</v>
       </c>
       <c r="G53">
-        <v>-8.519651297856408</v>
+        <v>-8.425473676657225</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.077841892429848</v>
       </c>
       <c r="E54">
-        <v>-14.5191954401003</v>
+        <v>-13.06400201705349</v>
       </c>
       <c r="F54">
-        <v>5.703911644128923</v>
+        <v>3.705576345698258</v>
       </c>
       <c r="G54">
-        <v>-8.212788176395577</v>
+        <v>-7.445231704324032</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.809475527267972</v>
       </c>
       <c r="E55">
-        <v>-11.73641193459481</v>
+        <v>-12.46474905161847</v>
       </c>
       <c r="F55">
-        <v>5.430856897144123</v>
+        <v>4.098280480343419</v>
       </c>
       <c r="G55">
-        <v>-7.181116337339649</v>
+        <v>-8.137615390468699</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.544590026684732</v>
       </c>
       <c r="E56">
-        <v>-11.8750285239696</v>
+        <v>-13.33346886287991</v>
       </c>
       <c r="F56">
-        <v>5.48478361506637</v>
+        <v>4.768416455329775</v>
       </c>
       <c r="G56">
-        <v>-8.645102241738657</v>
+        <v>-8.484050043936431</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.285228298469185</v>
       </c>
       <c r="E57">
-        <v>-13.11573983259112</v>
+        <v>-12.99515109824087</v>
       </c>
       <c r="F57">
-        <v>5.920556227717884</v>
+        <v>4.177777243255282</v>
       </c>
       <c r="G57">
-        <v>-8.774887679300933</v>
+        <v>-7.997300512922165</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.03148997126031</v>
       </c>
       <c r="E58">
-        <v>-12.88131431863605</v>
+        <v>-12.12964197505086</v>
       </c>
       <c r="F58">
-        <v>6.058716313361202</v>
+        <v>4.131955272002025</v>
       </c>
       <c r="G58">
-        <v>-8.502710350944994</v>
+        <v>-8.51644554439283</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.7836732123264234</v>
       </c>
       <c r="E59">
-        <v>-12.22590374703191</v>
+        <v>-11.75326691485136</v>
       </c>
       <c r="F59">
-        <v>5.543529774538106</v>
+        <v>4.274962963686527</v>
       </c>
       <c r="G59">
-        <v>-9.063494084005011</v>
+        <v>-7.912812338988023</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.542309318677026</v>
       </c>
       <c r="E60">
-        <v>-11.09736726805439</v>
+        <v>-13.3013438682695</v>
       </c>
       <c r="F60">
-        <v>5.783842471559853</v>
+        <v>5.012388879537091</v>
       </c>
       <c r="G60">
-        <v>-8.392415369445819</v>
+        <v>-8.299307426475016</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.3080433213597177</v>
       </c>
       <c r="E61">
-        <v>-11.92311638945705</v>
+        <v>-11.6143152184</v>
       </c>
       <c r="F61">
-        <v>5.672123873413895</v>
+        <v>3.980595980162499</v>
       </c>
       <c r="G61">
-        <v>-7.857264539208184</v>
+        <v>-8.710782453694062</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.08477952499781942</v>
       </c>
       <c r="E62">
-        <v>-11.2527663821016</v>
+        <v>-11.14195915160792</v>
       </c>
       <c r="F62">
-        <v>5.582477953082932</v>
+        <v>4.751681777058419</v>
       </c>
       <c r="G62">
-        <v>-7.937214783725613</v>
+        <v>-8.143019562377106</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.1265683813248945</v>
       </c>
       <c r="E63">
-        <v>-10.43951584896011</v>
+        <v>-10.29040225683555</v>
       </c>
       <c r="F63">
-        <v>5.540965149059039</v>
+        <v>4.21618698298829</v>
       </c>
       <c r="G63">
-        <v>-7.797460995065744</v>
+        <v>-8.688230617915998</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.3246653930139954</v>
       </c>
       <c r="E64">
-        <v>-11.62527865397257</v>
+        <v>-9.583810871996716</v>
       </c>
       <c r="F64">
-        <v>5.431503023718307</v>
+        <v>4.344277434483177</v>
       </c>
       <c r="G64">
-        <v>-8.284279431732759</v>
+        <v>-8.683617220403418</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.5078500101093502</v>
       </c>
       <c r="E65">
-        <v>-10.38812219744706</v>
+        <v>-8.265205281969255</v>
       </c>
       <c r="F65">
-        <v>5.73279018852532</v>
+        <v>4.171942223269963</v>
       </c>
       <c r="G65">
-        <v>-7.800919402589399</v>
+        <v>-8.655529963854573</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.6751009478202209</v>
       </c>
       <c r="E66">
-        <v>-11.6753635764974</v>
+        <v>-9.75533135351124</v>
       </c>
       <c r="F66">
-        <v>5.478849190992714</v>
+        <v>4.038311650585152</v>
       </c>
       <c r="G66">
-        <v>-7.700701052499279</v>
+        <v>-7.665145735681135</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.8233244151510334</v>
       </c>
       <c r="E67">
-        <v>-10.74430932052038</v>
+        <v>-8.966625149491325</v>
       </c>
       <c r="F67">
-        <v>5.388162841203836</v>
+        <v>3.93299798919764</v>
       </c>
       <c r="G67">
-        <v>-8.069943477026712</v>
+        <v>-8.311234666843598</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.9507931765837285</v>
       </c>
       <c r="E68">
-        <v>-11.13918319704122</v>
+        <v>-9.904250221253479</v>
       </c>
       <c r="F68">
-        <v>4.96074845564657</v>
+        <v>4.661369849335606</v>
       </c>
       <c r="G68">
-        <v>-7.609765278200828</v>
+        <v>-8.275915597977734</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.055772432695172</v>
       </c>
       <c r="E69">
-        <v>-12.11969291765601</v>
+        <v>-10.70263830270179</v>
       </c>
       <c r="F69">
-        <v>5.452460719009133</v>
+        <v>3.43882216117915</v>
       </c>
       <c r="G69">
-        <v>-6.8353707403994</v>
+        <v>-7.559729930640856</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.136225357512943</v>
       </c>
       <c r="E70">
-        <v>-10.08680206545069</v>
+        <v>-10.06748359533396</v>
       </c>
       <c r="F70">
-        <v>5.079251382821456</v>
+        <v>4.230065450454793</v>
       </c>
       <c r="G70">
-        <v>-6.867474212137006</v>
+        <v>-6.849296244697683</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.190077100082033</v>
       </c>
       <c r="E71">
-        <v>-10.39368769200249</v>
+        <v>-9.281136726272045</v>
       </c>
       <c r="F71">
-        <v>5.037849580029536</v>
+        <v>3.699340395889983</v>
       </c>
       <c r="G71">
-        <v>-6.260149632477825</v>
+        <v>-7.736351524742646</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.214646234513422</v>
       </c>
       <c r="E72">
-        <v>-11.92566139184936</v>
+        <v>-11.69644815147712</v>
       </c>
       <c r="F72">
-        <v>5.112150822591041</v>
+        <v>4.227863649898151</v>
       </c>
       <c r="G72">
-        <v>-6.473524189266955</v>
+        <v>-5.963080957371938</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.20758422405984</v>
       </c>
       <c r="E73">
-        <v>-10.70639693612816</v>
+        <v>-11.53498993920764</v>
       </c>
       <c r="F73">
-        <v>4.5789605466355</v>
+        <v>3.270371993085065</v>
       </c>
       <c r="G73">
-        <v>-7.074958976226934</v>
+        <v>-6.464313800349593</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.166185944460378</v>
       </c>
       <c r="E74">
-        <v>-10.70210394276889</v>
+        <v>-10.2685297273785</v>
       </c>
       <c r="F74">
-        <v>4.782432431785143</v>
+        <v>3.271440587034676</v>
       </c>
       <c r="G74">
-        <v>-6.202275446612338</v>
+        <v>-7.073410239650876</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.088327270253812</v>
       </c>
       <c r="E75">
-        <v>-10.69611730013075</v>
+        <v>-9.562155709292037</v>
       </c>
       <c r="F75">
-        <v>4.485222491334707</v>
+        <v>4.666144559045343</v>
       </c>
       <c r="G75">
-        <v>-7.076097560108061</v>
+        <v>-5.165356934282857</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.9720985266868003</v>
       </c>
       <c r="E76">
-        <v>-10.53692332486511</v>
+        <v>-10.30654173819888</v>
       </c>
       <c r="F76">
-        <v>5.358228956736273</v>
+        <v>3.249773809247052</v>
       </c>
       <c r="G76">
-        <v>-5.915037311298549</v>
+        <v>-6.035113614266428</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8167174991196722</v>
       </c>
       <c r="E77">
-        <v>-10.0416441226462</v>
+        <v>-10.88154019684882</v>
       </c>
       <c r="F77">
-        <v>4.389691848974258</v>
+        <v>3.924676210269116</v>
       </c>
       <c r="G77">
-        <v>-6.155019293713216</v>
+        <v>-3.729474692540493</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.6245145935293878</v>
       </c>
       <c r="E78">
-        <v>-11.5622468242598</v>
+        <v>-10.83356554321156</v>
       </c>
       <c r="F78">
-        <v>4.635970448030967</v>
+        <v>3.698366235824291</v>
       </c>
       <c r="G78">
-        <v>-6.247628491006983</v>
+        <v>-4.171885076621984</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.3967443199862052</v>
       </c>
       <c r="E79">
-        <v>-12.37578265126378</v>
+        <v>-11.65786555293176</v>
       </c>
       <c r="F79">
-        <v>4.205837360657713</v>
+        <v>3.069794423640804</v>
       </c>
       <c r="G79">
-        <v>-5.276455815064097</v>
+        <v>-6.610666125565507</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.136412254255676</v>
       </c>
       <c r="E80">
-        <v>-13.55596637629878</v>
+        <v>-12.38747517115158</v>
       </c>
       <c r="F80">
-        <v>3.962999799792232</v>
+        <v>3.055740342284907</v>
       </c>
       <c r="G80">
-        <v>-3.213295885359567</v>
+        <v>-3.915638078937149</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.1526027298515948</v>
       </c>
       <c r="E81">
-        <v>-13.83047794216975</v>
+        <v>-12.44141382505694</v>
       </c>
       <c r="F81">
-        <v>4.530330409886752</v>
+        <v>3.150853487474346</v>
       </c>
       <c r="G81">
-        <v>-5.382324428679579</v>
+        <v>-5.265283255654187</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4658426797080829</v>
       </c>
       <c r="E82">
-        <v>-14.56734217574985</v>
+        <v>-13.55403724637151</v>
       </c>
       <c r="F82">
-        <v>4.254677902726772</v>
+        <v>3.021101330969443</v>
       </c>
       <c r="G82">
-        <v>-4.486009541393864</v>
+        <v>-4.367918377469449</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.7955333664328887</v>
       </c>
       <c r="E83">
-        <v>-14.31505183183452</v>
+        <v>-12.44619589360904</v>
       </c>
       <c r="F83">
-        <v>4.733424559500718</v>
+        <v>3.044083556192713</v>
       </c>
       <c r="G83">
-        <v>-3.586242809027612</v>
+        <v>-4.556542680035688</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.135619909159311</v>
       </c>
       <c r="E84">
-        <v>-15.33802052474523</v>
+        <v>-13.46578181643602</v>
       </c>
       <c r="F84">
-        <v>3.75276677990094</v>
+        <v>2.788451032423591</v>
       </c>
       <c r="G84">
-        <v>-4.305434075312943</v>
+        <v>-5.286256823862158</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.481698717440573</v>
       </c>
       <c r="E85">
-        <v>-16.06297940015917</v>
+        <v>-16.65549852474479</v>
       </c>
       <c r="F85">
-        <v>4.161753304215529</v>
+        <v>2.720470233145447</v>
       </c>
       <c r="G85">
-        <v>-3.881578999150113</v>
+        <v>-2.248777526739233</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.829966860652865</v>
       </c>
       <c r="E86">
-        <v>-17.9297386549191</v>
+        <v>-16.07658746455222</v>
       </c>
       <c r="F86">
-        <v>3.866813090448765</v>
+        <v>1.799393607359426</v>
       </c>
       <c r="G86">
-        <v>-4.287239701765822</v>
+        <v>-4.25280328149945</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.178135792753759</v>
       </c>
       <c r="E87">
-        <v>-17.78004994659556</v>
+        <v>-17.94799293364402</v>
       </c>
       <c r="F87">
-        <v>3.892798975874586</v>
+        <v>2.233537649697036</v>
       </c>
       <c r="G87">
-        <v>-4.408425057620794</v>
+        <v>-3.206552975054908</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.523027304964029</v>
       </c>
       <c r="E88">
-        <v>-19.75335513780795</v>
+        <v>-18.46394461970794</v>
       </c>
       <c r="F88">
-        <v>3.639586941656443</v>
+        <v>2.870616795107274</v>
       </c>
       <c r="G88">
-        <v>-3.68021371326855</v>
+        <v>-3.249080887686871</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.861543667131534</v>
       </c>
       <c r="E89">
-        <v>-19.59158446083195</v>
+        <v>-19.57033233231395</v>
       </c>
       <c r="F89">
-        <v>3.878261127955454</v>
+        <v>2.226976979866864</v>
       </c>
       <c r="G89">
-        <v>-3.661454969613204</v>
+        <v>-3.108903821445833</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.195222727431427</v>
       </c>
       <c r="E90">
-        <v>-22.58468388467568</v>
+        <v>-24.84897975867295</v>
       </c>
       <c r="F90">
-        <v>2.899914493409487</v>
+        <v>1.486323744614992</v>
       </c>
       <c r="G90">
-        <v>-3.594583674231721</v>
+        <v>-2.425979897057045</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.524443058990897</v>
       </c>
       <c r="E91">
-        <v>-24.10303140623346</v>
+        <v>-23.56164781014246</v>
       </c>
       <c r="F91">
-        <v>2.79998190667056</v>
+        <v>1.655691743791379</v>
       </c>
       <c r="G91">
-        <v>-4.642681308414231</v>
+        <v>-1.883124758597833</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.849749201218107</v>
       </c>
       <c r="E92">
-        <v>-26.02555428992384</v>
+        <v>-25.9639489295235</v>
       </c>
       <c r="F92">
-        <v>2.767036078326418</v>
+        <v>1.549423803155842</v>
       </c>
       <c r="G92">
-        <v>-3.472397545801118</v>
+        <v>-2.547992120744996</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.171323503060608</v>
       </c>
       <c r="E93">
-        <v>-24.74853820518283</v>
+        <v>-26.60306605164804</v>
       </c>
       <c r="F93">
-        <v>2.385977132629812</v>
+        <v>0.5504649025260141</v>
       </c>
       <c r="G93">
-        <v>-3.317694511716419</v>
+        <v>-2.983502095886975</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.485410587482281</v>
       </c>
       <c r="E94">
-        <v>-28.56159483217341</v>
+        <v>-29.18547363926213</v>
       </c>
       <c r="F94">
-        <v>2.527183953580627</v>
+        <v>1.117801311192353</v>
       </c>
       <c r="G94">
-        <v>-3.750198887909946</v>
+        <v>-3.273184741262551</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.79373257544939</v>
       </c>
       <c r="E95">
-        <v>-30.36969449887497</v>
+        <v>-31.40025970693355</v>
       </c>
       <c r="F95">
-        <v>2.001091129532272</v>
+        <v>0.259400619836949</v>
       </c>
       <c r="G95">
-        <v>-3.240188777260776</v>
+        <v>-1.614592867394437</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.096255614562331</v>
       </c>
       <c r="E96">
-        <v>-32.59916414351626</v>
+        <v>-33.64079467781259</v>
       </c>
       <c r="F96">
-        <v>1.821120027600051</v>
+        <v>0.360307366641568</v>
       </c>
       <c r="G96">
-        <v>-3.164307247477057</v>
+        <v>-3.564714714376096</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.389261179957738</v>
       </c>
       <c r="E97">
-        <v>-35.26723234545945</v>
+        <v>-34.09471306268244</v>
       </c>
       <c r="F97">
-        <v>0.9638873342825942</v>
+        <v>-0.5984450653585798</v>
       </c>
       <c r="G97">
-        <v>-3.615609741984643</v>
+        <v>-3.180021017525238</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.671511125384244</v>
       </c>
       <c r="E98">
-        <v>-35.46227598520682</v>
+        <v>-37.22204098458752</v>
       </c>
       <c r="F98">
-        <v>0.3295931600805679</v>
+        <v>-0.962448754598947</v>
       </c>
       <c r="G98">
-        <v>-4.902898584185993</v>
+        <v>-4.920751710690932</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.933210631911526</v>
       </c>
       <c r="E99">
-        <v>-39.26669454802777</v>
+        <v>-40.24739446455089</v>
       </c>
       <c r="F99">
-        <v>0.2372401350772567</v>
+        <v>-0.4645593555137069</v>
       </c>
       <c r="G99">
-        <v>-4.154616007554626</v>
+        <v>-1.558651321027464</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.177785639291823</v>
       </c>
       <c r="E100">
-        <v>-42.03755458147107</v>
+        <v>-42.05353330200713</v>
       </c>
       <c r="F100">
-        <v>0.1698607305335449</v>
+        <v>-1.329984602444851</v>
       </c>
       <c r="G100">
-        <v>-4.711134152587366</v>
+        <v>-4.129458881858364</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.390186730778537</v>
       </c>
       <c r="E101">
-        <v>-42.66924500622303</v>
+        <v>-44.87960449055196</v>
       </c>
       <c r="F101">
-        <v>-0.1641179538249514</v>
+        <v>-1.400993084580228</v>
       </c>
       <c r="G101">
-        <v>-4.295206507712154</v>
+        <v>-6.471949202918422</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.586359681783183</v>
       </c>
       <c r="E102">
-        <v>-45.07005852189254</v>
+        <v>-45.51643020482861</v>
       </c>
       <c r="F102">
-        <v>-0.6052045433654237</v>
+        <v>-1.671719290795759</v>
       </c>
       <c r="G102">
-        <v>-4.926359318336023</v>
+        <v>-4.47155904164607</v>
       </c>
     </row>
   </sheetData>
